--- a/docs/snapshot/downloads/moleg_legis.xlsx
+++ b/docs/snapshot/downloads/moleg_legis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,17 +471,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=87372&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=88084&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대통령령</t>
+          <t>총리령</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026.06.30</t>
+          <t>2026.08.13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026.08.10</t>
+          <t>2026.08.20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:16.444527+09:00</t>
+          <t>2026-08-13 12:15:11.945277+09:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:16.444527+09:00</t>
+          <t>2026-08-13 12:15:11.945277+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86980&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=87372&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026.06.02</t>
+          <t>2026.06.30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026.07.13</t>
+          <t>2026.08.10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86932&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86980&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026.06.01</t>
+          <t>2026.06.02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86700&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86932&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,22 +647,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>총리령</t>
+          <t>대통령령</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026.05.13</t>
+          <t>2026.06.01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.07.13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -679,17 +679,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85978&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86700&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -699,22 +699,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대통령령</t>
+          <t>총리령</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026.03.16</t>
+          <t>2026.05.13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026.04.27</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -731,17 +731,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85936&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85978&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -751,22 +751,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>총리령</t>
+          <t>대통령령</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026.03.11</t>
+          <t>2026.03.16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026.03.18</t>
+          <t>2026.04.27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -783,17 +783,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개인정보 보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=84820&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85936&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2026.03.11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025.12.19</t>
+          <t>2026.03.18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -835,17 +835,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+          <t>개인정보 보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=83132&amp;lawCd=2000000318612&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=84820&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대통령령</t>
+          <t>총리령</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025.06.23</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025.08.04</t>
+          <t>2025.12.19</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=82960&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=83132&amp;lawCd=2000000318612&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025.05.30</t>
+          <t>2025.06.23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025.07.09</t>
+          <t>2025.08.04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -939,50 +939,102 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=82960&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>개인정보보호위원회</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>대통령령</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025.05.30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025.07.09</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:16.444527+09:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:16.444527+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>개인정보 보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=81708&amp;lawCd=2000000315220&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>개인정보보호위원회</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>총리령</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2025.02.07</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2025.02.14</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:14:16.444527+09:00</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:16.444527+09:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:16.444527+09:00</t>
         </is>
